--- a/projects.xlsx
+++ b/projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiekw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB99F0D-C9B7-426E-8EA7-46914B86EF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73071642-B261-4232-BCC1-4D6AEB15E1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1110" windowWidth="26490" windowHeight="12810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="33">
   <si>
     <t>Category</t>
   </si>
@@ -56,9 +56,6 @@
     <t>https://www.youtube.com/watch?v=oi2QgPH61JM</t>
   </si>
   <si>
-    <t>Screenshot 2026-08-22 175001.png</t>
-  </si>
-  <si>
     <t>Audio Visual Language</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>8. Student Name (optional): shows as a small signature at the bottom of the book page for that project.</t>
+  </si>
+  <si>
+    <t>Screenshot 2026-10-08 001504.png</t>
   </si>
 </sst>
 </file>
@@ -507,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -552,7 +552,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -592,12 +592,12 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -612,12 +612,12 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -632,12 +632,12 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -652,12 +652,12 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -672,12 +672,12 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -692,12 +692,12 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -712,12 +712,12 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -732,12 +732,12 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -752,12 +752,12 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -772,12 +772,12 @@
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -792,12 +792,12 @@
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -812,12 +812,12 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -832,12 +832,12 @@
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -852,27 +852,90 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="D15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="D17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D11" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D16" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D17" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="D19" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="D20" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="D4" r:id="rId14" xr:uid="{53B9F5AA-2353-4443-89A3-47EEEB083FA5}"/>
-    <hyperlink ref="D6" r:id="rId15" xr:uid="{6F4411D5-DAEC-42BA-A8CD-E903F29DFE34}"/>
+    <hyperlink ref="D7" r:id="rId15" xr:uid="{6F4411D5-DAEC-42BA-A8CD-E903F29DFE34}"/>
     <hyperlink ref="D3" r:id="rId16" xr:uid="{F3629273-61C4-4A81-8FB2-83E78A5A030F}"/>
+    <hyperlink ref="D6" r:id="rId17" xr:uid="{64E7B8D1-00B7-43B9-A48D-986F83A26A58}"/>
+    <hyperlink ref="D9" r:id="rId18" xr:uid="{D06629D7-417C-40D5-AAE6-2E6255BC5030}"/>
+    <hyperlink ref="D10" r:id="rId19" xr:uid="{3B7C38EB-5E57-46A4-A939-3C0725B55E81}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -888,47 +951,47 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
